--- a/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,7</t>
+          <t>-1,03; 3,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,85</t>
+          <t>-3,08; 2,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,79</t>
+          <t>1,6; 7,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,73</t>
+          <t>-3,22; 4,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 53,87</t>
+          <t>-11,13; 51,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 26,02</t>
+          <t>-20,3; 24,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,89; 110,45</t>
+          <t>15,17; 108,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 23,58</t>
+          <t>-12,49; 23,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,61</t>
+          <t>-1,14; 1,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,63</t>
+          <t>0,26; 3,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,07</t>
+          <t>-1,76; 1,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 31,79</t>
+          <t>-1,21; 29,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 50,93</t>
+          <t>-27,16; 50,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 79,47</t>
+          <t>3,52; 77,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 26,08</t>
+          <t>-30,57; 25,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 427,74</t>
+          <t>-14,0; 356,56</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,71</t>
+          <t>-0,48; 4,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,3</t>
+          <t>-1,7; 4,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,84</t>
+          <t>-2,17; 2,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 0,85</t>
+          <t>-4,59; 0,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 249,45</t>
+          <t>-16,31; 291,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 183,06</t>
+          <t>-35,3; 161,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 118,91</t>
+          <t>-44,25; 119,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 16,47</t>
+          <t>-51,14; 13,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,35</t>
+          <t>0,13; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,07</t>
+          <t>0,38; 3,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,53</t>
+          <t>0,16; 2,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 21,55</t>
+          <t>-0,15; 21,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 53,59</t>
+          <t>2,07; 52,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 46,94</t>
+          <t>4,42; 46,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 49,69</t>
+          <t>2,12; 54,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 231,38</t>
+          <t>-1,49; 203,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,71</t>
+          <t>-1,28; 3,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,93</t>
+          <t>-2,73; 3,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,64</t>
+          <t>1,41; 7,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,74</t>
+          <t>-1,94; 6,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 51,94</t>
+          <t>-12,97; 47,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 24,71</t>
+          <t>-18,36; 28,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 108,04</t>
+          <t>13,07; 108,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 23,4</t>
+          <t>-8,05; 32,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>-6,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,61</t>
+          <t>-1,31; 1,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,56</t>
+          <t>0,17; 3,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,08</t>
+          <t>-1,72; 0,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 29,09</t>
+          <t>-2,34; 1,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 50,19</t>
+          <t>-28,69; 49,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 77,35</t>
+          <t>2,55; 74,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 25,14</t>
+          <t>-30,49; 23,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 356,56</t>
+          <t>-22,12; 12,93</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-26,21%</t>
+          <t>-21,48%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,89</t>
+          <t>-0,58; 4,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,1</t>
+          <t>-1,83; 4,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,88</t>
+          <t>-2,06; 2,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,71</t>
+          <t>-4,45; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 291,43</t>
+          <t>-21,81; 281,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 161,26</t>
+          <t>-34,6; 169,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 119,92</t>
+          <t>-42,99; 107,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 13,61</t>
+          <t>-48,6; 20,81</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,4</t>
+          <t>0,04; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,12</t>
+          <t>0,43; 3,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,74</t>
+          <t>0,28; 2,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 21,0</t>
+          <t>-0,97; 1,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 52,83</t>
+          <t>0,69; 54,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 46,38</t>
+          <t>5,47; 48,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 54,17</t>
+          <t>4,78; 54,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 203,75</t>
+          <t>-8,21; 19,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
